--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T10:14:31+00:00</t>
+    <t>2026-07-08T15:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T15:46:54+00:00</t>
+    <t>2026-07-09T09:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:13:13+00:00</t>
+    <t>2026-07-10T12:01:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:01:50+00:00</t>
+    <t>2026-07-10T12:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:28:44+00:00</t>
+    <t>2026-07-10T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:58:40+00:00</t>
+    <t>2026-07-20T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:08:41+00:00</t>
+    <t>2026-07-21T09:08:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:08:11+00:00</t>
+    <t>2026-07-21T09:10:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:10:59+00:00</t>
+    <t>2026-07-22T09:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:27:19+00:00</t>
+    <t>2026-07-28T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T07:28:06+00:00</t>
+    <t>2026-07-30T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:11:50+00:00</t>
+    <t>2026-08-03T07:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$54</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="373">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T07:00:21+00:00</t>
+    <t>2026-08-04T07:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -993,6 +993,91 @@
   </si>
   <si>
     <t>SPM-27</t>
+  </si>
+  <si>
+    <t>Specimen.container.type.id</t>
+  </si>
+  <si>
+    <t>Specimen.container.type.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Specimen.container.type.extension:device</t>
+  </si>
+  <si>
+    <t>device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Specimen.container.device|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>R5: `Specimen.container.device` (new:Reference(Device))</t>
+  </si>
+  <si>
+    <t>Element `Specimen.container.device` has a context of Specimen.container based on following the parent source element upwards and mapping to `Specimen`.
+Element `Specimen.container.device` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
+  </si>
+  <si>
+    <t>Specimen.container.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Specimen.container.type.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Specimen.container.capacity</t>
@@ -1404,10 +1489,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM49"/>
+  <dimension ref="A1:AM54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.40234375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="34.4921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="32.40234375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1435,7 +1520,7 @@
     <col min="26" max="26" width="65.70703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="31.46875" customWidth="true" bestFit="true" hidden="true"/>
@@ -6327,13 +6412,13 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>316</v>
+        <v>210</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>317</v>
+        <v>211</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6384,7 +6469,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>315</v>
+        <v>212</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6396,35 +6481,35 @@
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>318</v>
+        <v>213</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>319</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>76</v>
@@ -6436,15 +6521,17 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>241</v>
+        <v>131</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>321</v>
+        <v>132</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6481,62 +6568,64 @@
         <v>76</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>76</v>
+        <v>317</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>76</v>
+        <v>318</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>76</v>
+        <v>319</v>
       </c>
       <c r="AF46" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AG46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
-        <v>325</v>
-      </c>
       <c r="B47" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>76</v>
@@ -6545,15 +6634,17 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>327</v>
+        <v>295</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -6578,13 +6669,13 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>249</v>
+        <v>76</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>329</v>
+        <v>76</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>330</v>
+        <v>76</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>76</v>
@@ -6602,36 +6693,36 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>325</v>
+        <v>216</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>331</v>
+        <v>76</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>332</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6654,19 +6745,19 @@
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>165</v>
+        <v>326</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -6691,13 +6782,13 @@
         <v>76</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>169</v>
+        <v>76</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>338</v>
+        <v>76</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>339</v>
+        <v>76</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>76</v>
@@ -6715,7 +6806,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6730,21 +6821,21 @@
         <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>76</v>
+        <v>332</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6755,7 +6846,7 @@
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>76</v>
@@ -6764,19 +6855,23 @@
         <v>76</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>342</v>
+        <v>209</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>50</v>
+        <v>335</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
       </c>
@@ -6824,13 +6919,13 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>76</v>
@@ -6839,17 +6934,566 @@
         <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM49" t="s" s="2">
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK50" t="s" s="2">
         <v>345</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>372</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM49">
+  <autoFilter ref="A1:AM54">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6859,7 +7503,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI48">
+  <conditionalFormatting sqref="A2:AI53">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:50:37+00:00</t>
+    <t>2026-08-04T08:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:17:33+00:00</t>
+    <t>2026-08-06T12:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:56:12+00:00</t>
+    <t>2026-08-07T08:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:15:28+00:00</t>
+    <t>2026-08-07T09:41:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:41:31+00:00</t>
+    <t>2026-08-07T12:53:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T12:53:43+00:00</t>
+    <t>2026-09-03T14:46:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -546,7 +546,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-specimen-type-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-specimen-type-cisis|20260716085852</t>
   </si>
   <si>
     <t>.code</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:46:57+00:00</t>
+    <t>2026-09-04T09:26:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:26:41+00:00</t>
+    <t>2026-09-04T11:53:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
